--- a/slide_classification/SurGen_Results/Averaging/Conch1_5/1-MSIH/Output/cross_valid_avg_eval_metrics.xlsx
+++ b/slide_classification/SurGen_Results/Averaging/Conch1_5/1-MSIH/Output/cross_valid_avg_eval_metrics.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet name="baseline" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -467,19 +468,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.8782051282051282</v>
+        <v>0.8589743589743589</v>
       </c>
       <c r="C2" t="n">
-        <v>0.8846153846153846</v>
+        <v>0.8993288590604027</v>
       </c>
       <c r="D2" t="n">
-        <v>0.8709677419354839</v>
+        <v>0.8773006134969326</v>
       </c>
       <c r="E2" t="n">
-        <v>0.8967741935483871</v>
+        <v>0.8961038961038961</v>
       </c>
       <c r="F2" t="n">
-        <v>0.8826406120760959</v>
+        <v>0.8829269319088975</v>
       </c>
     </row>
     <row r="3">
@@ -489,19 +490,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.5453900709219859</v>
+        <v>0.5892857142857143</v>
       </c>
       <c r="C3" t="n">
-        <v>0.548936170212766</v>
+        <v>0.5603174603174603</v>
       </c>
       <c r="D3" t="n">
-        <v>0.5714285714285714</v>
+        <v>0.4831081081081081</v>
       </c>
       <c r="E3" t="n">
-        <v>0.555952380952381</v>
+        <v>0.645083932853717</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5554267983789261</v>
+        <v>0.56944880389125</v>
       </c>
     </row>
     <row r="4">
@@ -511,19 +512,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.5540845494207913</v>
+        <v>0.5943262411347517</v>
       </c>
       <c r="C4" t="n">
-        <v>0.5598746081504702</v>
+        <v>0.5783814374646293</v>
       </c>
       <c r="D4" t="n">
-        <v>0.5801733477789816</v>
+        <v>0.4673202614379085</v>
       </c>
       <c r="E4" t="n">
-        <v>0.5724137931034483</v>
+        <v>0.6639388979814512</v>
       </c>
       <c r="F4" t="n">
-        <v>0.5666365746134229</v>
+        <v>0.5759917095046853</v>
       </c>
     </row>
     <row r="5">
@@ -533,19 +534,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.8611461503743737</v>
+        <v>0.8547735951991273</v>
       </c>
       <c r="C5" t="n">
-        <v>0.8652278755727031</v>
+        <v>0.8771094221806953</v>
       </c>
       <c r="D5" t="n">
-        <v>0.8619508614965224</v>
+        <v>0.8486306588074903</v>
       </c>
       <c r="E5" t="n">
-        <v>0.8727474972191324</v>
+        <v>0.8888487399125697</v>
       </c>
       <c r="F5" t="n">
-        <v>0.8652680961656829</v>
+        <v>0.8673406040249707</v>
       </c>
     </row>
     <row r="6">
@@ -555,19 +556,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.8170212765957447</v>
+        <v>0.7441964285714286</v>
       </c>
       <c r="C6" t="n">
-        <v>0.8373522458628841</v>
+        <v>0.7116402116402116</v>
       </c>
       <c r="D6" t="n">
-        <v>0.7761904761904761</v>
+        <v>0.6351351351351351</v>
       </c>
       <c r="E6" t="n">
-        <v>0.6576190476190477</v>
+        <v>0.6489208633093524</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7720457615670382</v>
+        <v>0.6849731596640319</v>
       </c>
     </row>
     <row r="7">
@@ -578,31 +579,27 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>[[135   6]
- [ 13   2]]</t>
+          <t>[[130, 10], [12, 4]]</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>[[136   5]
- [ 13   2]]</t>
+          <t>[[132, 3], [12, 2]]</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>[[132   8]
- [ 12   3]]</t>
+          <t>[[143, 5], [15, 0]]</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>[[137   3]
- [ 13   2]]</t>
+          <t>[[133, 6], [10, 5]]</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>[[135, 6], [13, 2]]</t>
+          <t>[[134, 6], [12, 3]]</t>
         </is>
       </c>
     </row>
@@ -613,19 +610,19 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.7628205128205128</v>
+        <v>0.782051282051282</v>
       </c>
       <c r="C8" t="n">
-        <v>0.7692307692307693</v>
+        <v>0.7516778523489933</v>
       </c>
       <c r="D8" t="n">
-        <v>0.8387096774193549</v>
+        <v>0.6748466257668712</v>
       </c>
       <c r="E8" t="n">
-        <v>0.8387096774193549</v>
+        <v>0.7987012987012987</v>
       </c>
       <c r="F8" t="n">
-        <v>0.802367659222498</v>
+        <v>0.7518192647171114</v>
       </c>
     </row>
     <row r="9">
@@ -635,19 +632,19 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.6304964539007092</v>
+        <v>0.5464285714285715</v>
       </c>
       <c r="C9" t="n">
-        <v>0.7829787234042553</v>
+        <v>0.6388888888888888</v>
       </c>
       <c r="D9" t="n">
-        <v>0.7321428571428572</v>
+        <v>0.5813063063063063</v>
       </c>
       <c r="E9" t="n">
-        <v>0.7619047619047619</v>
+        <v>0.5316546762589928</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7268806990881459</v>
+        <v>0.5745696107206899</v>
       </c>
     </row>
     <row r="10">
@@ -657,19 +654,19 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.5663736759071445</v>
+        <v>0.5322751322751322</v>
       </c>
       <c r="C10" t="n">
-        <v>0.6285714285714286</v>
+        <v>0.5623561165356832</v>
       </c>
       <c r="D10" t="n">
-        <v>0.6624858461806463</v>
+        <v>0.5021610096236961</v>
       </c>
       <c r="E10" t="n">
-        <v>0.6750524109014675</v>
+        <v>0.5238855091253616</v>
       </c>
       <c r="F10" t="n">
-        <v>0.6331208403901717</v>
+        <v>0.5301694418899683</v>
       </c>
     </row>
     <row r="11">
@@ -679,19 +676,19 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.8021098802031865</v>
+        <v>0.8039614706281374</v>
       </c>
       <c r="C11" t="n">
-        <v>0.8131868131868131</v>
+        <v>0.796110504631709</v>
       </c>
       <c r="D11" t="n">
-        <v>0.859164229259562</v>
+        <v>0.7414025403220532</v>
       </c>
       <c r="E11" t="n">
-        <v>0.8610265773990667</v>
+        <v>0.8151432690178079</v>
       </c>
       <c r="F11" t="n">
-        <v>0.8338718750121571</v>
+        <v>0.7891544461499269</v>
       </c>
     </row>
     <row r="12">
@@ -701,19 +698,19 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.6628841607565013</v>
+        <v>0.6334821428571429</v>
       </c>
       <c r="C12" t="n">
-        <v>0.830260047281324</v>
+        <v>0.68994708994709</v>
       </c>
       <c r="D12" t="n">
-        <v>0.740952380952381</v>
+        <v>0.6581081081081082</v>
       </c>
       <c r="E12" t="n">
-        <v>0.7338095238095238</v>
+        <v>0.5453237410071943</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7419765281999324</v>
+        <v>0.6317152704798839</v>
       </c>
     </row>
     <row r="13">
@@ -724,31 +721,27 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>[[112  29]
- [  8   7]]</t>
+          <t>[[118, 22], [12, 4]]</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>[[108  33]
- [  3  12]]</t>
+          <t>[[105, 30], [7, 7]]</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>[[121  19]
- [  6   9]]</t>
+          <t>[[103, 45], [8, 7]]</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>[[120  20]
- [  5  10]]</t>
+          <t>[[120, 19], [12, 3]]</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>[[115, 25], [6, 10]]</t>
+          <t>[[112, 29], [10, 5]]</t>
         </is>
       </c>
     </row>
@@ -759,19 +752,19 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.8910256410256411</v>
+        <v>0.8974358974358975</v>
       </c>
       <c r="C14" t="n">
-        <v>0.9102564102564102</v>
+        <v>0.8590604026845637</v>
       </c>
       <c r="D14" t="n">
-        <v>0.8967741935483871</v>
+        <v>0.901840490797546</v>
       </c>
       <c r="E14" t="n">
-        <v>0.8774193548387097</v>
+        <v>0.9090909090909091</v>
       </c>
       <c r="F14" t="n">
-        <v>0.893868899917287</v>
+        <v>0.8918569250022291</v>
       </c>
     </row>
     <row r="15">
@@ -781,19 +774,19 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.5226950354609929</v>
+        <v>0.5830357142857143</v>
       </c>
       <c r="C15" t="n">
-        <v>0.5631205673758866</v>
+        <v>0.4740740740740741</v>
       </c>
       <c r="D15" t="n">
-        <v>0.6154761904761905</v>
+        <v>0.5265765765765766</v>
       </c>
       <c r="E15" t="n">
-        <v>0.4857142857142857</v>
+        <v>0.5333333333333333</v>
       </c>
       <c r="F15" t="n">
-        <v>0.5467515197568389</v>
+        <v>0.5292549245674246</v>
       </c>
     </row>
     <row r="16">
@@ -803,19 +796,19 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.5236213400395187</v>
+        <v>0.6087774294670847</v>
       </c>
       <c r="C16" t="n">
-        <v>0.5873015873015872</v>
+        <v>0.4620938628158845</v>
       </c>
       <c r="D16" t="n">
-        <v>0.6386946386946387</v>
+        <v>0.5295815295815296</v>
       </c>
       <c r="E16" t="n">
-        <v>0.4673539518900344</v>
+        <v>0.538527397260274</v>
       </c>
       <c r="F16" t="n">
-        <v>0.5542428794814448</v>
+        <v>0.5347450547811932</v>
       </c>
     </row>
     <row r="17">
@@ -825,19 +818,19 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.8615260256179962</v>
+        <v>0.875894220721807</v>
       </c>
       <c r="C17" t="n">
-        <v>0.8821733821733821</v>
+        <v>0.8373512950354954</v>
       </c>
       <c r="D17" t="n">
-        <v>0.8849537559214978</v>
+        <v>0.8710328526279445</v>
       </c>
       <c r="E17" t="n">
-        <v>0.8442523001884491</v>
+        <v>0.8714975093399752</v>
       </c>
       <c r="F17" t="n">
-        <v>0.8682263659753313</v>
+        <v>0.8639439694313056</v>
       </c>
     </row>
     <row r="18">
@@ -847,19 +840,19 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.6510638297872341</v>
+        <v>0.6267857142857142</v>
       </c>
       <c r="C18" t="n">
-        <v>0.7125295508274231</v>
+        <v>0.4978835978835979</v>
       </c>
       <c r="D18" t="n">
-        <v>0.6595238095238096</v>
+        <v>0.5792792792792792</v>
       </c>
       <c r="E18" t="n">
-        <v>0.5364285714285714</v>
+        <v>0.652757793764988</v>
       </c>
       <c r="F18" t="n">
-        <v>0.6398864403917596</v>
+        <v>0.5891765963033948</v>
       </c>
     </row>
     <row r="19">
@@ -870,31 +863,27 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>[[138   3]
- [ 14   1]]</t>
+          <t>[[137, 3], [13, 3]]</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>[[140   1]
- [ 13   2]]</t>
+          <t>[[128, 7], [14, 0]]</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>[[135   5]
- [ 11   4]]</t>
+          <t>[[146, 2], [14, 1]]</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>[[136   4]
- [ 15   0]]</t>
+          <t>[[139, 0], [14, 1]]</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>[[137, 3], [13, 2]]</t>
+          <t>[[138, 3], [14, 1]]</t>
         </is>
       </c>
     </row>
@@ -905,19 +894,19 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.6025641025641025</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="C20" t="n">
-        <v>0.6410256410256411</v>
+        <v>0.6375838926174496</v>
       </c>
       <c r="D20" t="n">
-        <v>0.6838709677419355</v>
+        <v>0.5705521472392638</v>
       </c>
       <c r="E20" t="n">
-        <v>0.5935483870967742</v>
+        <v>0.6298701298701299</v>
       </c>
       <c r="F20" t="n">
-        <v>0.6302522746071133</v>
+        <v>0.6261682090983776</v>
       </c>
     </row>
     <row r="21">
@@ -927,19 +916,19 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.5716312056737589</v>
+        <v>0.6205357142857143</v>
       </c>
       <c r="C21" t="n">
-        <v>0.5631205673758866</v>
+        <v>0.5439153439153439</v>
       </c>
       <c r="D21" t="n">
-        <v>0.6464285714285714</v>
+        <v>0.5538288288288289</v>
       </c>
       <c r="E21" t="n">
-        <v>0.5666666666666667</v>
+        <v>0.5868105515587529</v>
       </c>
       <c r="F21" t="n">
-        <v>0.5869617527862209</v>
+        <v>0.57627260964716</v>
       </c>
     </row>
     <row r="22">
@@ -949,19 +938,19 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.4700854700854701</v>
+        <v>0.521133412042503</v>
       </c>
       <c r="C22" t="n">
-        <v>0.4842975206611571</v>
+        <v>0.4745297805642633</v>
       </c>
       <c r="D22" t="n">
-        <v>0.5335053129414655</v>
+        <v>0.4471899224806202</v>
       </c>
       <c r="E22" t="n">
-        <v>0.4649021864211738</v>
+        <v>0.4883124453512095</v>
       </c>
       <c r="F22" t="n">
-        <v>0.4881976225273166</v>
+        <v>0.482791390109649</v>
       </c>
     </row>
     <row r="23">
@@ -971,19 +960,19 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.6840894148586457</v>
+        <v>0.7309720582447856</v>
       </c>
       <c r="C23" t="n">
-        <v>0.7139224411951685</v>
+        <v>0.7122351728345712</v>
       </c>
       <c r="D23" t="n">
-        <v>0.7470928907830422</v>
+        <v>0.6602701288819138</v>
       </c>
       <c r="E23" t="n">
-        <v>0.6764913322692009</v>
+        <v>0.7050180364665938</v>
       </c>
       <c r="F23" t="n">
-        <v>0.7053990197765143</v>
+        <v>0.702123849106966</v>
       </c>
     </row>
     <row r="24">
@@ -993,19 +982,19 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.6070921985815603</v>
+        <v>0.7441964285714285</v>
       </c>
       <c r="C24" t="n">
-        <v>0.6260047281323877</v>
+        <v>0.6708994708994709</v>
       </c>
       <c r="D24" t="n">
-        <v>0.7409523809523809</v>
+        <v>0.5900900900900901</v>
       </c>
       <c r="E24" t="n">
-        <v>0.6399999999999999</v>
+        <v>0.6244604316546762</v>
       </c>
       <c r="F24" t="n">
-        <v>0.6535123269165821</v>
+        <v>0.6574116053039165</v>
       </c>
     </row>
     <row r="25">
@@ -1016,31 +1005,27 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>[[86 55]
- [ 7  8]]</t>
+          <t>[[95, 45], [7, 9]]</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>[[93 48]
- [ 8  7]]</t>
+          <t>[[89, 46], [8, 6]]</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>[[97 43]
- [ 6  9]]</t>
+          <t>[[85, 63], [7, 8]]</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>[[84 56]
- [ 7  8]]</t>
+          <t>[[89, 50], [7, 8]]</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>[[90, 50], [7, 8]]</t>
+          <t>[[90, 51], [7, 8]]</t>
         </is>
       </c>
     </row>
@@ -1051,19 +1036,19 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.8974358974358975</v>
+        <v>0.8910256410256411</v>
       </c>
       <c r="C26" t="n">
-        <v>0.8974358974358975</v>
+        <v>0.8657718120805369</v>
       </c>
       <c r="D26" t="n">
-        <v>0.9161290322580645</v>
+        <v>0.8895705521472392</v>
       </c>
       <c r="E26" t="n">
-        <v>0.8709677419354839</v>
+        <v>0.8896103896103896</v>
       </c>
       <c r="F26" t="n">
-        <v>0.8954921422663359</v>
+        <v>0.8839945987159517</v>
       </c>
     </row>
     <row r="27">
@@ -1073,19 +1058,19 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.5560283687943263</v>
+        <v>0.5241071428571429</v>
       </c>
       <c r="C27" t="n">
-        <v>0.5858156028368794</v>
+        <v>0.4777777777777778</v>
       </c>
       <c r="D27" t="n">
-        <v>0.5666666666666667</v>
+        <v>0.4898648648648649</v>
       </c>
       <c r="E27" t="n">
-        <v>0.4821428571428572</v>
+        <v>0.4928057553956834</v>
       </c>
       <c r="F27" t="n">
-        <v>0.5476633738601824</v>
+        <v>0.4961388852238673</v>
       </c>
     </row>
     <row r="28">
@@ -1095,19 +1080,19 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.5726027397260274</v>
+        <v>0.5236213400395187</v>
       </c>
       <c r="C28" t="n">
-        <v>0.6087774294670847</v>
+        <v>0.4640287769784173</v>
       </c>
       <c r="D28" t="n">
-        <v>0.5954627584822325</v>
+        <v>0.4707792207792208</v>
       </c>
       <c r="E28" t="n">
-        <v>0.4655172413793103</v>
+        <v>0.4707903780068728</v>
       </c>
       <c r="F28" t="n">
-        <v>0.5605900422636637</v>
+        <v>0.4823049289510074</v>
       </c>
     </row>
     <row r="29">
@@ -1117,19 +1102,19 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.8735511064278187</v>
+        <v>0.8561624591802425</v>
       </c>
       <c r="C29" t="n">
-        <v>0.8802025560646251</v>
+        <v>0.8408575153300178</v>
       </c>
       <c r="D29" t="n">
-        <v>0.885921339800921</v>
+        <v>0.8549119592064377</v>
       </c>
       <c r="E29" t="n">
-        <v>0.8409343715239154</v>
+        <v>0.8498683447137055</v>
       </c>
       <c r="F29" t="n">
-        <v>0.87015234345432</v>
+        <v>0.8504500696076008</v>
       </c>
     </row>
     <row r="30">
@@ -1139,19 +1124,19 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.7513002364066195</v>
+        <v>0.7549107142857143</v>
       </c>
       <c r="C30" t="n">
-        <v>0.8122931442080379</v>
+        <v>0.6952380952380952</v>
       </c>
       <c r="D30" t="n">
-        <v>0.7971428571428572</v>
+        <v>0.690990990990991</v>
       </c>
       <c r="E30" t="n">
-        <v>0.5780952380952381</v>
+        <v>0.6609112709832135</v>
       </c>
       <c r="F30" t="n">
-        <v>0.7347078689631881</v>
+        <v>0.7005127678745036</v>
       </c>
     </row>
     <row r="31">
@@ -1162,31 +1147,413 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>[[138   3]
- [ 13   2]]</t>
+          <t>[[138, 2], [15, 1]]</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>[[137   4]
- [ 12   3]]</t>
+          <t>[[129, 6], [14, 0]]</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>[[140   0]
- [ 13   2]]</t>
+          <t>[[145, 3], [15, 0]]</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>[[135   5]
- [ 15   0]]</t>
+          <t>[[137, 2], [15, 0]]</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>[[138, 3], [13, 2]]</t>
+          <t>[[137, 3], [15, 0]]</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:P6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Method</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Model</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Classifier</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>N_folds</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>N_test</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>acc</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>acc_sd</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>bacc</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>bacc_sd</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>macro_f1</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>macro_f1_sd</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>weighted_f1</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>weighted_f1_sd</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>auroc</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>auroc_sd</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>conf_matrix</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Averaging</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Conch1_5</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>lin</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>4</v>
+      </c>
+      <c r="E2" t="n">
+        <v>622</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.8829269319088975</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.01618669831016168</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.56944880389125</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.0584214706485267</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0.5759917095046853</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0.07050896651439872</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0.8673406040249707</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0.01632499217755542</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0.6849731596640319</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0.04472729592364895</v>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>[[134, 6], [12, 3]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Averaging</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Conch1_5</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>ann</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>4</v>
+      </c>
+      <c r="E3" t="n">
+        <v>622</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.7518192647171114</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.04753079824442775</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.5745696107206899</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.04127942073171488</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0.5301694418899683</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0.02158921053299385</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0.7891544461499269</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.02838704875357998</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0.6317152704798839</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0.05374510414716677</v>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>[[112, 29], [10, 5]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Averaging</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Conch1_5</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>knn</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>4</v>
+      </c>
+      <c r="E4" t="n">
+        <v>622</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.8918569250022291</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.01938697116046657</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.5292549245674246</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.03860410136861859</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.5347450547811932</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0.05196141910766339</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.8639439694313056</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.01547002801835828</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0.5891765963033948</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.05892661298346235</v>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>[[138, 3], [14, 1]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Averaging</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Conch1_5</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>proto</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>4</v>
+      </c>
+      <c r="E5" t="n">
+        <v>622</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.6261682090983776</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.03491881101116996</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.57627260964716</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.03008731707479234</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.482791390109649</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0.02662851566695473</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.702123849106966</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.02595461546205886</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0.6574116053039165</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.05773104520845974</v>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>[[90, 51], [7, 8]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Averaging</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Conch1_5</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>rf</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>4</v>
+      </c>
+      <c r="E6" t="n">
+        <v>622</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.8839945987159517</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.01053724196313288</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.4961388852238673</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.01710136535195967</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.4823049289510074</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0.02401296727013513</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.8504500696076008</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.006018624320440401</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0.7005127678745036</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.03408042523292692</v>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>[[137, 3], [15, 0]]</t>
         </is>
       </c>
     </row>

--- a/slide_classification/SurGen_Results/Averaging/Conch1_5/1-MSIH/Output/cross_valid_avg_eval_metrics.xlsx
+++ b/slide_classification/SurGen_Results/Averaging/Conch1_5/1-MSIH/Output/cross_valid_avg_eval_metrics.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="baseline" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Summary" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="baseline" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -619,10 +619,10 @@
         <v>0.6748466257668712</v>
       </c>
       <c r="E8" t="n">
-        <v>0.7987012987012987</v>
+        <v>0.7272727272727273</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7518192647171114</v>
+        <v>0.7339621218599686</v>
       </c>
     </row>
     <row r="9">
@@ -641,10 +641,10 @@
         <v>0.5813063063063063</v>
       </c>
       <c r="E9" t="n">
-        <v>0.5316546762589928</v>
+        <v>0.5218225419664269</v>
       </c>
       <c r="F9" t="n">
-        <v>0.5745696107206899</v>
+        <v>0.5721115771475485</v>
       </c>
     </row>
     <row r="10">
@@ -663,10 +663,10 @@
         <v>0.5021610096236961</v>
       </c>
       <c r="E10" t="n">
-        <v>0.5238855091253616</v>
+        <v>0.4986046511627907</v>
       </c>
       <c r="F10" t="n">
-        <v>0.5301694418899683</v>
+        <v>0.5238492273993256</v>
       </c>
     </row>
     <row r="11">
@@ -685,10 +685,10 @@
         <v>0.7414025403220532</v>
       </c>
       <c r="E11" t="n">
-        <v>0.8151432690178079</v>
+        <v>0.771247357293869</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7891544461499269</v>
+        <v>0.7781804682189422</v>
       </c>
     </row>
     <row r="12">
@@ -707,10 +707,10 @@
         <v>0.6581081081081082</v>
       </c>
       <c r="E12" t="n">
-        <v>0.5453237410071943</v>
+        <v>0.6057553956834533</v>
       </c>
       <c r="F12" t="n">
-        <v>0.6317152704798839</v>
+        <v>0.6468231841489486</v>
       </c>
     </row>
     <row r="13">
@@ -736,12 +736,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>[[120, 19], [12, 3]]</t>
+          <t>[[108, 31], [11, 4]]</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>[[112, 29], [10, 5]]</t>
+          <t>[[108, 32], [10, 6]]</t>
         </is>
       </c>
     </row>
@@ -1348,38 +1348,38 @@
         <v>622</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7518192647171114</v>
+        <v>0.7339621218599686</v>
       </c>
       <c r="G3" t="n">
-        <v>0.04753079824442775</v>
+        <v>0.03926131783620616</v>
       </c>
       <c r="H3" t="n">
-        <v>0.5745696107206899</v>
+        <v>0.5721115771475485</v>
       </c>
       <c r="I3" t="n">
-        <v>0.04127942073171488</v>
+        <v>0.04396690872096922</v>
       </c>
       <c r="J3" t="n">
-        <v>0.5301694418899683</v>
+        <v>0.5238492273993256</v>
       </c>
       <c r="K3" t="n">
-        <v>0.02158921053299385</v>
+        <v>0.02579459150471871</v>
       </c>
       <c r="L3" t="n">
-        <v>0.7891544461499269</v>
+        <v>0.7781804682189422</v>
       </c>
       <c r="M3" t="n">
-        <v>0.02838704875357998</v>
+        <v>0.02442759862570513</v>
       </c>
       <c r="N3" t="n">
-        <v>0.6317152704798839</v>
+        <v>0.6468231841489486</v>
       </c>
       <c r="O3" t="n">
-        <v>0.05374510414716677</v>
+        <v>0.03103049867568729</v>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>[[112, 29], [10, 5]]</t>
+          <t>[[108, 32], [10, 6]]</t>
         </is>
       </c>
     </row>
